--- a/fixtures/jeju/timetables/bis/raw/405134.xlsx
+++ b/fixtures/jeju/timetables/bis/raw/405134.xlsx
@@ -8,8 +8,8 @@
   <sheets>
     <sheet name="705 월평-제주대-첨단-함덕 (평일)" r:id="rId3" sheetId="1"/>
     <sheet name="705 함덕-첨단-제주대-월평 (평일)" r:id="rId4" sheetId="2"/>
-    <sheet name="705 함덕-첨단-제주대-월평 (휴일)" r:id="rId5" sheetId="3"/>
-    <sheet name="705 월평-제주대-첨단-함덕 (휴일)" r:id="rId6" sheetId="4"/>
+    <sheet name="705 월평-제주대-첨단-함덕 (휴일)" r:id="rId5" sheetId="3"/>
+    <sheet name="705 함덕-첨단-제주대-월평 (휴일)" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
@@ -1054,362 +1054,362 @@
     <t>첫차 6:30, 막차 20:00, 배차간격 20분~90분, 제주시 공영버스(064-728-3211)</t>
   </si>
   <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:17</t>
+    <t>06:44</t>
+  </si>
+  <si>
+    <t>06:52</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>07:13</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>09:16</t>
   </si>
   <si>
     <t>09:22</t>
   </si>
   <si>
-    <t>09:28</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>09:42</t>
-  </si>
-  <si>
-    <t>09:59</t>
-  </si>
-  <si>
-    <t>10:04</t>
-  </si>
-  <si>
-    <t>10:12</t>
+    <t>09:26</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>10:08</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:16</t>
   </si>
   <si>
     <t>10:26</t>
   </si>
   <si>
-    <t>10:52</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:36</t>
+    <t>10:43</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>11:15</t>
   </si>
   <si>
     <t>11:30</t>
   </si>
   <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:19</t>
-  </si>
-  <si>
-    <t>12:24</t>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>12:27</t>
   </si>
   <si>
     <t>12:32</t>
   </si>
   <si>
-    <t>14:07</t>
-  </si>
-  <si>
-    <t>14:12</t>
-  </si>
-  <si>
-    <t>14:18</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>14:49</t>
-  </si>
-  <si>
-    <t>14:54</t>
-  </si>
-  <si>
-    <t>15:00</t>
+    <t>12:38</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>13:13</t>
+  </si>
+  <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>14:57</t>
   </si>
   <si>
     <t>15:02</t>
   </si>
   <si>
-    <t>15:16</t>
-  </si>
-  <si>
-    <t>15:07</t>
-  </si>
-  <si>
-    <t>15:18</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>15:49</t>
-  </si>
-  <si>
-    <t>15:54</t>
-  </si>
-  <si>
-    <t>16:02</t>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:44</t>
+  </si>
+  <si>
+    <t>15:46</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>16:32</t>
+  </si>
+  <si>
+    <t>16:38</t>
+  </si>
+  <si>
+    <t>16:45</t>
   </si>
   <si>
     <t>16:30</t>
   </si>
   <si>
-    <t>16:37</t>
-  </si>
-  <si>
-    <t>16:42</t>
-  </si>
-  <si>
-    <t>16:48</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>17:24</t>
-  </si>
-  <si>
-    <t>18:07</t>
-  </si>
-  <si>
-    <t>18:18</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>18:49</t>
-  </si>
-  <si>
-    <t>18:54</t>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>16:52</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
+    <t>17:13</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>17:27</t>
+  </si>
+  <si>
+    <t>17:38</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:44</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>19:56</t>
+  </si>
+  <si>
+    <t>20:13</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>20:27</t>
+  </si>
+  <si>
+    <t>20:38</t>
+  </si>
+  <si>
+    <t>20:45</t>
   </si>
   <si>
     <t>705번
 (휴일)</t>
   </si>
   <si>
+    <t>첫차 6:30, 막차 20:00, 배차간격 30분~90분, 제주시 공영버스(064-728-3211)</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:17</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>09:59</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>11:37</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>14:07</t>
+  </si>
+  <si>
+    <t>14:12</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>15:18</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>15:49</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>16:37</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>16:48</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>18:07</t>
+  </si>
+  <si>
+    <t>18:18</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>18:49</t>
+  </si>
+  <si>
+    <t>18:54</t>
+  </si>
+  <si>
     <t>첫차 6:30, 막차 20:00, 배차간격 50분~110분, 제주시 공영버스(064-728-3211)</t>
-  </si>
-  <si>
-    <t>06:44</t>
-  </si>
-  <si>
-    <t>06:52</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>07:13</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:14</t>
-  </si>
-  <si>
-    <t>09:16</t>
-  </si>
-  <si>
-    <t>09:26</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>09:57</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>10:08</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:16</t>
-  </si>
-  <si>
-    <t>10:43</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>11:08</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>11:46</t>
-  </si>
-  <si>
-    <t>11:52</t>
-  </si>
-  <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>12:38</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>12:44</t>
-  </si>
-  <si>
-    <t>12:52</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>13:13</t>
-  </si>
-  <si>
-    <t>13:27</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>14:26</t>
-  </si>
-  <si>
-    <t>14:43</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:44</t>
-  </si>
-  <si>
-    <t>15:46</t>
-  </si>
-  <si>
-    <t>16:13</t>
-  </si>
-  <si>
-    <t>16:32</t>
-  </si>
-  <si>
-    <t>16:38</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>16:44</t>
-  </si>
-  <si>
-    <t>16:46</t>
-  </si>
-  <si>
-    <t>16:52</t>
-  </si>
-  <si>
-    <t>16:56</t>
-  </si>
-  <si>
-    <t>17:13</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>17:27</t>
-  </si>
-  <si>
-    <t>17:38</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>19:44</t>
-  </si>
-  <si>
-    <t>19:52</t>
-  </si>
-  <si>
-    <t>19:56</t>
-  </si>
-  <si>
-    <t>20:13</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>20:27</t>
-  </si>
-  <si>
-    <t>20:38</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>첫차 6:30, 막차 20:00, 배차간격 30분~90분, 제주시 공영버스(064-728-3211)</t>
   </si>
 </sst>
 </file>
@@ -3741,13 +3741,13 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="33" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
       <c r="E2" s="33"/>
       <c r="F2" s="36" t="s">
-        <v>342</v>
+        <v>202</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="3" ht="50.0" customHeight="true">
       <c r="B3" s="34" t="s">
-        <v>343</v>
+        <v>203</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="38" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -3829,37 +3829,37 @@
         <v>0</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>206</v>
+        <v>1</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H7" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I7" s="41" t="s">
-        <v>207</v>
+        <v>7</v>
       </c>
       <c r="J7" s="41" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K7" s="41" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L7" s="41" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N7" s="42" t="s">
         <v>12</v>
@@ -3873,34 +3873,34 @@
         <v>208</v>
       </c>
       <c r="D8" s="44" t="s">
-        <v>209</v>
+        <v>345</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>210</v>
+        <v>346</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>211</v>
+        <v>347</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="J8" s="44" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="N8" s="45" t="s">
         <v>24</v>
@@ -3911,37 +3911,37 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>223</v>
+        <v>36</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>215</v>
+        <v>37</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>224</v>
+        <v>38</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>226</v>
+        <v>41</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>227</v>
+        <v>45</v>
       </c>
       <c r="N9" s="45" t="s">
         <v>24</v>
@@ -3952,37 +3952,37 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>240</v>
+        <v>357</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N10" s="45" t="s">
         <v>24</v>
@@ -3993,37 +3993,37 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>63</v>
+        <v>360</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>64</v>
+        <v>238</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>65</v>
+        <v>361</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>66</v>
+        <v>239</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>67</v>
+        <v>362</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>75</v>
+        <v>367</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="N11" s="45" t="s">
         <v>24</v>
@@ -4034,37 +4034,37 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>363</v>
+        <v>90</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>85</v>
+        <v>373</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>364</v>
+        <v>98</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>93</v>
+        <v>375</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>101</v>
+        <v>377</v>
       </c>
       <c r="N12" s="45" t="s">
         <v>24</v>
@@ -4075,37 +4075,37 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>263</v>
+        <v>93</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>264</v>
+        <v>378</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>261</v>
+        <v>101</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>265</v>
+        <v>379</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>266</v>
+        <v>380</v>
       </c>
       <c r="H13" s="44" t="s">
+        <v>381</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="K13" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="I13" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>269</v>
-      </c>
-      <c r="K13" s="44" t="s">
-        <v>270</v>
-      </c>
       <c r="L13" s="44" t="s">
-        <v>271</v>
+        <v>383</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>272</v>
+        <v>384</v>
       </c>
       <c r="N13" s="45" t="s">
         <v>24</v>
@@ -4119,34 +4119,34 @@
         <v>270</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>368</v>
+        <v>272</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>369</v>
+        <v>116</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>372</v>
+        <v>278</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="N14" s="45" t="s">
         <v>24</v>
@@ -4157,37 +4157,37 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>284</v>
+        <v>394</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>379</v>
+        <v>289</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>127</v>
+        <v>395</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>380</v>
+        <v>292</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>381</v>
+        <v>295</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>135</v>
+        <v>396</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>141</v>
+        <v>398</v>
       </c>
       <c r="N15" s="45" t="s">
         <v>24</v>
@@ -4198,37 +4198,37 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>147</v>
+        <v>404</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>160</v>
+        <v>306</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>306</v>
+        <v>407</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>162</v>
+        <v>408</v>
       </c>
       <c r="N16" s="45" t="s">
         <v>24</v>
@@ -4239,37 +4239,37 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>309</v>
+        <v>159</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>390</v>
+        <v>170</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>312</v>
+        <v>171</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>391</v>
+        <v>166</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>392</v>
+        <v>172</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>393</v>
+        <v>174</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>394</v>
+        <v>175</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="N17" s="45" t="s">
         <v>24</v>
@@ -4280,37 +4280,37 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>326</v>
+        <v>409</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>182</v>
+        <v>324</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>327</v>
+        <v>410</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>328</v>
+        <v>411</v>
       </c>
       <c r="H18" s="44" t="s">
-        <v>329</v>
+        <v>412</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>330</v>
+        <v>413</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>331</v>
+        <v>414</v>
       </c>
       <c r="K18" s="44" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="L18" s="44" t="s">
-        <v>333</v>
+        <v>415</v>
       </c>
       <c r="M18" s="44" t="s">
-        <v>194</v>
+        <v>416</v>
       </c>
       <c r="N18" s="45" t="s">
         <v>24</v>
@@ -4324,34 +4324,34 @@
         <v>190</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>334</v>
+        <v>191</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>335</v>
+        <v>193</v>
       </c>
       <c r="G19" s="47" t="s">
-        <v>336</v>
+        <v>194</v>
       </c>
       <c r="H19" s="47" t="s">
-        <v>337</v>
+        <v>195</v>
       </c>
       <c r="I19" s="47" t="s">
-        <v>338</v>
+        <v>196</v>
       </c>
       <c r="J19" s="47" t="s">
-        <v>339</v>
+        <v>197</v>
       </c>
       <c r="K19" s="47" t="s">
-        <v>340</v>
+        <v>198</v>
       </c>
       <c r="L19" s="47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M19" s="47" t="s">
-        <v>341</v>
+        <v>200</v>
       </c>
       <c r="N19" s="48" t="s">
         <v>24</v>
@@ -4391,13 +4391,13 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="49" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
       <c r="E2" s="49"/>
       <c r="F2" s="52" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="G2" s="49"/>
       <c r="H2" s="49"/>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="3" ht="50.0" customHeight="true">
       <c r="B3" s="50" t="s">
-        <v>203</v>
+        <v>343</v>
       </c>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
@@ -4479,37 +4479,37 @@
         <v>0</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" s="57" t="s">
         <v>6</v>
       </c>
       <c r="I7" s="57" t="s">
-        <v>7</v>
+        <v>207</v>
       </c>
       <c r="J7" s="57" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K7" s="57" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L7" s="57" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M7" s="57" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N7" s="58" t="s">
         <v>12</v>
@@ -4523,34 +4523,34 @@
         <v>208</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>397</v>
+        <v>209</v>
       </c>
       <c r="E8" s="60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" s="60" t="s">
-        <v>398</v>
+        <v>210</v>
       </c>
       <c r="G8" s="60" t="s">
-        <v>399</v>
+        <v>211</v>
       </c>
       <c r="H8" s="60" t="s">
-        <v>400</v>
+        <v>212</v>
       </c>
       <c r="I8" s="60" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="J8" s="60" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="K8" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="60" t="s">
         <v>215</v>
       </c>
-      <c r="L8" s="60" t="s">
-        <v>224</v>
-      </c>
       <c r="M8" s="60" t="s">
-        <v>225</v>
+        <v>37</v>
       </c>
       <c r="N8" s="61" t="s">
         <v>24</v>
@@ -4561,37 +4561,37 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="60" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="D9" s="60" t="s">
-        <v>36</v>
+        <v>223</v>
       </c>
       <c r="E9" s="60" t="s">
-        <v>37</v>
+        <v>215</v>
       </c>
       <c r="F9" s="60" t="s">
+        <v>224</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>225</v>
+      </c>
+      <c r="H9" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="60" t="s">
-        <v>40</v>
-      </c>
       <c r="I9" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="60" t="s">
-        <v>43</v>
-      </c>
       <c r="L9" s="60" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M9" s="60" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="N9" s="61" t="s">
         <v>24</v>
@@ -4602,37 +4602,37 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="60" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="D10" s="60" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="E10" s="60" t="s">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>347</v>
+        <v>421</v>
       </c>
       <c r="G10" s="60" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="H10" s="60" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="I10" s="60" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="J10" s="60" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="K10" s="60" t="s">
-        <v>408</v>
+        <v>240</v>
       </c>
       <c r="L10" s="60" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="M10" s="60" t="s">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="N10" s="61" t="s">
         <v>24</v>
@@ -4643,37 +4643,37 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>411</v>
+        <v>63</v>
       </c>
       <c r="D11" s="60" t="s">
-        <v>238</v>
+        <v>64</v>
       </c>
       <c r="E11" s="60" t="s">
-        <v>412</v>
+        <v>65</v>
       </c>
       <c r="F11" s="60" t="s">
-        <v>239</v>
+        <v>66</v>
       </c>
       <c r="G11" s="60" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="H11" s="60" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="I11" s="60" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="J11" s="60" t="s">
-        <v>415</v>
+        <v>79</v>
       </c>
       <c r="K11" s="60" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="L11" s="60" t="s">
-        <v>417</v>
+        <v>75</v>
       </c>
       <c r="M11" s="60" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="N11" s="61" t="s">
         <v>24</v>
@@ -4684,37 +4684,37 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="E12" s="60" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="F12" s="60" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="G12" s="60" t="s">
-        <v>90</v>
+        <v>434</v>
       </c>
       <c r="H12" s="60" t="s">
-        <v>422</v>
+        <v>85</v>
       </c>
       <c r="I12" s="60" t="s">
-        <v>98</v>
+        <v>435</v>
       </c>
       <c r="J12" s="60" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K12" s="60" t="s">
-        <v>366</v>
+        <v>93</v>
       </c>
       <c r="L12" s="60" t="s">
-        <v>424</v>
+        <v>375</v>
       </c>
       <c r="M12" s="60" t="s">
-        <v>425</v>
+        <v>101</v>
       </c>
       <c r="N12" s="61" t="s">
         <v>24</v>
@@ -4725,37 +4725,37 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>93</v>
+        <v>263</v>
       </c>
       <c r="D13" s="60" t="s">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="E13" s="60" t="s">
-        <v>101</v>
+        <v>261</v>
       </c>
       <c r="F13" s="60" t="s">
-        <v>427</v>
+        <v>265</v>
       </c>
       <c r="G13" s="60" t="s">
-        <v>428</v>
+        <v>266</v>
       </c>
       <c r="H13" s="60" t="s">
-        <v>429</v>
+        <v>267</v>
       </c>
       <c r="I13" s="60" t="s">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="J13" s="60" t="s">
-        <v>430</v>
+        <v>269</v>
       </c>
       <c r="K13" s="60" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L13" s="60" t="s">
-        <v>431</v>
+        <v>271</v>
       </c>
       <c r="M13" s="60" t="s">
-        <v>432</v>
+        <v>272</v>
       </c>
       <c r="N13" s="61" t="s">
         <v>24</v>
@@ -4769,34 +4769,34 @@
         <v>270</v>
       </c>
       <c r="D14" s="60" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>272</v>
+        <v>438</v>
       </c>
       <c r="F14" s="60" t="s">
-        <v>116</v>
+        <v>439</v>
       </c>
       <c r="G14" s="60" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="H14" s="60" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="I14" s="60" t="s">
-        <v>278</v>
+        <v>442</v>
       </c>
       <c r="J14" s="60" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K14" s="60" t="s">
-        <v>375</v>
+        <v>444</v>
       </c>
       <c r="L14" s="60" t="s">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="M14" s="60" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N14" s="61" t="s">
         <v>24</v>
@@ -4807,37 +4807,37 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D15" s="60" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>441</v>
+        <v>284</v>
       </c>
       <c r="F15" s="60" t="s">
-        <v>290</v>
+        <v>447</v>
       </c>
       <c r="G15" s="60" t="s">
-        <v>289</v>
+        <v>448</v>
       </c>
       <c r="H15" s="60" t="s">
-        <v>442</v>
+        <v>127</v>
       </c>
       <c r="I15" s="60" t="s">
-        <v>292</v>
+        <v>449</v>
       </c>
       <c r="J15" s="60" t="s">
-        <v>295</v>
+        <v>450</v>
       </c>
       <c r="K15" s="60" t="s">
-        <v>443</v>
+        <v>135</v>
       </c>
       <c r="L15" s="60" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="M15" s="60" t="s">
-        <v>445</v>
+        <v>141</v>
       </c>
       <c r="N15" s="61" t="s">
         <v>24</v>
@@ -4848,37 +4848,37 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F16" s="60" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="G16" s="60" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="H16" s="60" t="s">
-        <v>450</v>
+        <v>147</v>
       </c>
       <c r="I16" s="60" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="J16" s="60" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K16" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="L16" s="60" t="s">
         <v>306</v>
       </c>
-      <c r="L16" s="60" t="s">
-        <v>453</v>
-      </c>
       <c r="M16" s="60" t="s">
-        <v>454</v>
+        <v>162</v>
       </c>
       <c r="N16" s="61" t="s">
         <v>24</v>
@@ -4889,37 +4889,37 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>159</v>
+        <v>309</v>
       </c>
       <c r="D17" s="60" t="s">
-        <v>170</v>
+        <v>458</v>
       </c>
       <c r="E17" s="60" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="F17" s="60" t="s">
-        <v>166</v>
+        <v>459</v>
       </c>
       <c r="G17" s="60" t="s">
-        <v>172</v>
+        <v>460</v>
       </c>
       <c r="H17" s="60" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I17" s="60" t="s">
-        <v>174</v>
+        <v>461</v>
       </c>
       <c r="J17" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="K17" s="60" t="s">
+        <v>179</v>
+      </c>
+      <c r="L17" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="K17" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="L17" s="60" t="s">
-        <v>177</v>
-      </c>
       <c r="M17" s="60" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N17" s="61" t="s">
         <v>24</v>
@@ -4930,37 +4930,37 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>455</v>
+        <v>326</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>324</v>
+        <v>182</v>
       </c>
       <c r="F18" s="60" t="s">
-        <v>456</v>
+        <v>327</v>
       </c>
       <c r="G18" s="60" t="s">
-        <v>457</v>
+        <v>328</v>
       </c>
       <c r="H18" s="60" t="s">
-        <v>458</v>
+        <v>329</v>
       </c>
       <c r="I18" s="60" t="s">
-        <v>459</v>
+        <v>330</v>
       </c>
       <c r="J18" s="60" t="s">
-        <v>460</v>
+        <v>331</v>
       </c>
       <c r="K18" s="60" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L18" s="60" t="s">
-        <v>461</v>
+        <v>333</v>
       </c>
       <c r="M18" s="60" t="s">
-        <v>462</v>
+        <v>194</v>
       </c>
       <c r="N18" s="61" t="s">
         <v>24</v>
@@ -4974,34 +4974,34 @@
         <v>190</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>191</v>
+        <v>334</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="F19" s="63" t="s">
-        <v>193</v>
+        <v>335</v>
       </c>
       <c r="G19" s="63" t="s">
-        <v>194</v>
+        <v>336</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>195</v>
+        <v>337</v>
       </c>
       <c r="I19" s="63" t="s">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="J19" s="63" t="s">
-        <v>197</v>
+        <v>339</v>
       </c>
       <c r="K19" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="L19" s="63" t="s">
         <v>198</v>
       </c>
-      <c r="L19" s="63" t="s">
-        <v>199</v>
-      </c>
       <c r="M19" s="63" t="s">
-        <v>200</v>
+        <v>341</v>
       </c>
       <c r="N19" s="64" t="s">
         <v>24</v>
